--- a/temp/espc-2/searchByMAC-11.xlsx
+++ b/temp/espc-2/searchByMAC-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="51">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,39 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
 </sst>
 </file>
@@ -484,13 +517,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AM212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,17 +543,21 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -528,11 +565,9 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -548,15 +583,13 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -566,15 +599,21 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>18</v>
+      </c>
+      <c r="W4">
+        <v>19</v>
+      </c>
+      <c r="AF4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -588,15 +627,42 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="W5">
+        <v>11</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="1"/>
+      <c r="AF5">
+        <v>11</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI5" s="1"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -610,15 +676,42 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>11</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="W6">
+        <v>11</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" s="1"/>
+      <c r="AF6">
+        <v>11</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI6" s="1"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>3</v>
@@ -632,15 +725,39 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="W7">
+        <v>11</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="1"/>
+      <c r="AF7">
+        <v>11</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI7" s="1"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
@@ -654,18 +771,39 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z8" s="1"/>
+      <c r="AF8">
+        <v>11</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI8" s="1"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -676,18 +814,45 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>11</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="W9">
+        <v>11</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="1"/>
+      <c r="AF9">
+        <v>11</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI9" s="1"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -695,40 +860,106 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>11</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF10">
+        <v>11</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="2"/>
+      <c r="J11" s="1"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="1"/>
+      <c r="L11" s="2"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W11">
+        <v>11</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF11">
+        <v>11</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>3</v>
@@ -742,15 +973,57 @@
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
@@ -764,15 +1037,57 @@
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
@@ -786,15 +1101,57 @@
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1">
+        <v>6</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14">
+        <v>11</v>
+      </c>
+      <c r="X14" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF14">
+        <v>11</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>6</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
@@ -808,15 +1165,57 @@
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>13</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>13</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
@@ -830,15 +1229,61 @@
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1">
+        <v>14</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>14</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -848,15 +1293,64 @@
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W17">
+        <v>11</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF17">
+        <v>11</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -864,23 +1358,72 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -890,15 +1433,75 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19">
+        <v>11</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF19">
+        <v>11</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>18</v>
@@ -912,15 +1515,75 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>18</v>
@@ -934,15 +1597,84 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>18</v>
@@ -953,18 +1685,87 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>18</v>
@@ -975,18 +1776,42 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N23">
+        <v>11</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W23">
+        <v>11</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF23">
+        <v>11</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
@@ -1000,15 +1825,48 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>18</v>
@@ -1022,15 +1880,48 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>18</v>
@@ -1044,15 +1935,48 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF26">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>18</v>
@@ -1066,15 +1990,33 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="1"/>
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27" s="1">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z27" s="1"/>
+      <c r="AF27">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>19</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI27" s="1"/>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>18</v>
@@ -1088,15 +2030,24 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="1"/>
+      <c r="Z28" s="1"/>
+      <c r="AF28">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>20</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI28" s="1"/>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>18</v>
@@ -1110,15 +2061,12 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>18</v>
@@ -1132,15 +2080,12 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>18</v>
@@ -1154,15 +2099,25 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N31">
+        <v>18</v>
+      </c>
+      <c r="W31">
+        <v>19</v>
+      </c>
+      <c r="AF31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1172,15 +2127,16 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1192,19 +2148,20 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="B34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1214,15 +2171,22 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>19</v>
@@ -1236,15 +2200,26 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>19</v>
@@ -1262,11 +2237,11 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>19</v>
@@ -1284,14 +2259,14 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -1306,14 +2281,14 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1328,11 +2303,11 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>19</v>
@@ -1350,11 +2325,11 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>19</v>
@@ -1372,11 +2347,11 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>19</v>
@@ -1394,14 +2369,14 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -1416,14 +2391,14 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -1438,11 +2413,11 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>19</v>
@@ -1460,11 +2435,11 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>19</v>
@@ -1479,14 +2454,18 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="C47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -1497,14 +2476,12 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1519,19 +2496,14 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1545,14 +2517,14 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -1570,17 +2542,17 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -1592,8 +2564,8 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -1602,10 +2574,10 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -1617,8 +2589,8 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -1627,10 +2599,10 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -1652,7 +2624,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>23</v>
@@ -1677,10 +2649,10 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -1702,7 +2674,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
@@ -1727,7 +2699,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
@@ -1752,7 +2724,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>21</v>
@@ -1777,10 +2749,10 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -1794,15 +2766,18 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -1821,7 +2796,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>21</v>
@@ -1842,8 +2817,12 @@
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="C62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -1859,9 +2838,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -1876,22 +2853,14 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="B64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1915,10 +2884,10 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -1943,10 +2912,10 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -1971,10 +2940,10 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -1999,7 +2968,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>25</v>
@@ -2027,10 +2996,10 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -2055,10 +3024,10 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -2073,8 +3042,8 @@
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="R70" s="1"/>
-      <c r="S70" s="2"/>
-      <c r="T70" s="2"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
@@ -2083,10 +3052,10 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -2101,8 +3070,8 @@
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
@@ -2111,7 +3080,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>24</v>
@@ -2139,7 +3108,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>24</v>
@@ -2160,17 +3129,17 @@
       <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="V73" s="1"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -2181,18 +3150,24 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
       <c r="P74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="2"/>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -2211,7 +3186,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>24</v>
@@ -2232,8 +3207,12 @@
     <row r="77" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
+      <c r="C77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -2249,9 +3228,7 @@
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -2263,28 +3240,17 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
-      <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
-      <c r="AB78" s="1"/>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="B79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -2301,8 +3267,8 @@
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
       <c r="V79" s="1"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
@@ -2311,10 +3277,10 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -2332,8 +3298,8 @@
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
       <c r="V80" s="1"/>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
+      <c r="W80" s="2"/>
+      <c r="X80" s="2"/>
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
@@ -2342,10 +3308,10 @@
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -2373,10 +3339,10 @@
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -2404,10 +3370,10 @@
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -2435,7 +3401,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>26</v>
@@ -2466,10 +3432,10 @@
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -2490,17 +3456,17 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -2517,15 +3483,21 @@
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
       <c r="T86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="2"/>
+      <c r="AB86" s="2"/>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -2539,12 +3511,15 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
       <c r="P87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>27</v>
@@ -2566,7 +3541,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>27</v>
@@ -2588,10 +3563,10 @@
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -2610,10 +3585,10 @@
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -2631,8 +3606,12 @@
     <row r="92" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
+      <c r="C92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
@@ -2648,9 +3627,7 @@
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -2665,25 +3642,14 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
-      <c r="R93" s="1"/>
-      <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
-      <c r="V93" s="1"/>
-      <c r="W93" s="1"/>
-      <c r="X93" s="1"/>
-      <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
-      <c r="AB93" s="1"/>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -2710,10 +3676,10 @@
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -2741,10 +3707,10 @@
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -2772,10 +3738,10 @@
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -2803,10 +3769,10 @@
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -2834,7 +3800,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>28</v>
@@ -2865,7 +3831,7 @@
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>28</v>
@@ -2896,10 +3862,10 @@
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -2927,7 +3893,7 @@
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>29</v>
@@ -2958,7 +3924,7 @@
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>29</v>
@@ -2989,10 +3955,10 @@
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -3013,14 +3979,14 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="2"/>
-      <c r="AB104" s="2"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>28</v>
@@ -3037,15 +4003,24 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
       <c r="P105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Z105" s="1"/>
+      <c r="AA105" s="2"/>
+      <c r="AB105" s="2"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -3063,8 +4038,12 @@
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="C107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -3080,15 +4059,11 @@
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
-      <c r="B108" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
@@ -3099,31 +4074,24 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
       <c r="P108" s="1"/>
-      <c r="R108" s="1"/>
-      <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
-      <c r="V108" s="1"/>
-      <c r="W108" s="1"/>
-      <c r="X108" s="1"/>
-      <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B109" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
+      <c r="F109" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
+      <c r="J109" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
@@ -3144,7 +4112,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>5</v>
@@ -3175,10 +4143,10 @@
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -3186,8 +4154,8 @@
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
@@ -3206,10 +4174,10 @@
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -3217,8 +4185,8 @@
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
@@ -3237,7 +4205,7 @@
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>5</v>
@@ -3268,7 +4236,7 @@
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>5</v>
@@ -3292,14 +4260,14 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="2"/>
-      <c r="AB114" s="2"/>
+      <c r="AA114" s="1"/>
+      <c r="AB114" s="1"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>5</v>
@@ -3323,17 +4291,17 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AA115" s="2"/>
+      <c r="AB115" s="2"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -3361,7 +4329,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>30</v>
@@ -3392,19 +4360,15 @@
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
       <c r="I118" s="1"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
@@ -3427,15 +4391,19 @@
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
+      <c r="G119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="I119" s="1"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
@@ -3458,7 +4426,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>5</v>
@@ -3475,15 +4443,24 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
       <c r="P120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Z120" s="1"/>
+      <c r="AA120" s="1"/>
+      <c r="AB120" s="1"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -3501,16 +4478,24 @@
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="C122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
+      <c r="K122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
@@ -3518,9 +4503,7 @@
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
-      <c r="B123" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -3538,19 +4521,19 @@
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="B124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
+      <c r="J124" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
@@ -3562,7 +4545,7 @@
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>33</v>
@@ -3584,7 +4567,7 @@
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>33</v>
@@ -3595,8 +4578,12 @@
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
+      <c r="K126" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
@@ -3606,7 +4593,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>33</v>
@@ -3628,7 +4615,7 @@
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>33</v>
@@ -3650,7 +4637,7 @@
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>33</v>
@@ -3672,7 +4659,7 @@
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>33</v>
@@ -3694,7 +4681,7 @@
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>33</v>
@@ -3716,7 +4703,7 @@
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>33</v>
@@ -3738,7 +4725,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>33</v>
@@ -3760,7 +4747,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>33</v>
@@ -3782,7 +4769,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>33</v>
@@ -3804,7 +4791,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>33</v>
@@ -3825,8 +4812,12 @@
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="C137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -3842,15 +4833,11 @@
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
-      <c r="B138" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
-      <c r="F138" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="F138" s="1"/>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
@@ -3864,11 +4851,15 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
+      <c r="B139" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
+      <c r="F139" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
@@ -3883,20 +4874,12 @@
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
-      <c r="C140" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="G140" s="1"/>
+      <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1"/>
       <c r="K140" s="1"/>
@@ -3909,12 +4892,20 @@
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="C141" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-      <c r="H141" s="1"/>
+      <c r="G141" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="I141" s="1"/>
       <c r="J141" s="1"/>
       <c r="K141" s="1"/>
@@ -4124,9 +5115,7 @@
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
-      <c r="B153" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -4144,13 +5133,11 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="B154" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
@@ -4168,7 +5155,7 @@
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>35</v>
@@ -4190,7 +5177,7 @@
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>35</v>
@@ -4212,7 +5199,7 @@
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>35</v>
@@ -4223,8 +5210,8 @@
       <c r="H157" s="1"/>
       <c r="I157" s="1"/>
       <c r="J157" s="1"/>
-      <c r="K157" s="2"/>
-      <c r="L157" s="2"/>
+      <c r="K157" s="1"/>
+      <c r="L157" s="1"/>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
@@ -4234,7 +5221,7 @@
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>35</v>
@@ -4245,8 +5232,8 @@
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
       <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
-      <c r="L158" s="1"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
       <c r="M158" s="1"/>
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
@@ -4256,7 +5243,7 @@
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>35</v>
@@ -4278,7 +5265,7 @@
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>35</v>
@@ -4300,7 +5287,7 @@
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>35</v>
@@ -4322,7 +5309,7 @@
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>35</v>
@@ -4344,7 +5331,7 @@
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>35</v>
@@ -4366,7 +5353,7 @@
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>35</v>
@@ -4388,7 +5375,7 @@
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>35</v>
@@ -4410,7 +5397,7 @@
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>35</v>
@@ -4431,8 +5418,12 @@
     <row r="167" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="C167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
@@ -4448,9 +5439,7 @@
     </row>
     <row r="168" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
-      <c r="B168" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -4465,19 +5454,14 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
       <c r="P168" s="1"/>
-      <c r="R168" s="1"/>
-      <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
     </row>
     <row r="169" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
@@ -4498,7 +5482,7 @@
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>36</v>
@@ -4523,7 +5507,7 @@
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>36</v>
@@ -4548,7 +5532,7 @@
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>36</v>
@@ -4573,7 +5557,7 @@
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>36</v>
@@ -4598,7 +5582,7 @@
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>36</v>
@@ -4623,7 +5607,7 @@
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>36</v>
@@ -4648,7 +5632,7 @@
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>36</v>
@@ -4673,7 +5657,7 @@
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>36</v>
@@ -4698,7 +5682,7 @@
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>36</v>
@@ -4723,10 +5707,10 @@
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
@@ -4741,17 +5725,17 @@
       <c r="O179" s="1"/>
       <c r="P179" s="1"/>
       <c r="R179" s="1"/>
-      <c r="S179" s="2"/>
-      <c r="T179" s="2"/>
+      <c r="S179" s="1"/>
+      <c r="T179" s="1"/>
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
@@ -4766,14 +5750,14 @@
       <c r="O180" s="1"/>
       <c r="P180" s="1"/>
       <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="S180" s="2"/>
+      <c r="T180" s="2"/>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>36</v>
@@ -4788,8 +5772,8 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
       <c r="N181" s="1"/>
-      <c r="O181" s="2"/>
-      <c r="P181" s="2"/>
+      <c r="O181" s="1"/>
+      <c r="P181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
       <c r="T181" s="1"/>
@@ -4797,8 +5781,12 @@
     <row r="182" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="C182" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
@@ -4809,14 +5797,15 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
       <c r="N182" s="1"/>
-      <c r="O182" s="1"/>
-      <c r="P182" s="1"/>
+      <c r="O182" s="2"/>
+      <c r="P182" s="2"/>
+      <c r="R182" s="1"/>
+      <c r="S182" s="1"/>
+      <c r="T182" s="1"/>
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
-      <c r="B183" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -4831,19 +5820,14 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
       <c r="P183" s="1"/>
-      <c r="R183" s="1"/>
-      <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="B184" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
@@ -4864,7 +5848,7 @@
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>38</v>
@@ -4889,7 +5873,7 @@
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>38</v>
@@ -4914,7 +5898,7 @@
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>38</v>
@@ -4939,7 +5923,7 @@
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>38</v>
@@ -4957,14 +5941,14 @@
       <c r="O188" s="1"/>
       <c r="P188" s="1"/>
       <c r="R188" s="1"/>
-      <c r="S188" s="2"/>
-      <c r="T188" s="2"/>
+      <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>38</v>
@@ -4982,14 +5966,14 @@
       <c r="O189" s="1"/>
       <c r="P189" s="1"/>
       <c r="R189" s="1"/>
-      <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="S189" s="2"/>
+      <c r="T189" s="2"/>
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>38</v>
@@ -5014,7 +5998,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>38</v>
@@ -5039,7 +6023,7 @@
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>38</v>
@@ -5064,7 +6048,7 @@
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>38</v>
@@ -5089,7 +6073,7 @@
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>38</v>
@@ -5114,7 +6098,7 @@
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>38</v>
@@ -5139,7 +6123,7 @@
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>38</v>
@@ -5156,12 +6140,19 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
       <c r="P196" s="1"/>
+      <c r="R196" s="1"/>
+      <c r="S196" s="1"/>
+      <c r="T196" s="1"/>
     </row>
     <row r="197" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="C197" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
@@ -5177,9 +6168,7 @@
     </row>
     <row r="198" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
-      <c r="B198" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -5197,13 +6186,11 @@
     </row>
     <row r="199" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
-      <c r="B199" s="1"/>
-      <c r="C199" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="B199" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
@@ -5221,7 +6208,7 @@
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>39</v>
@@ -5243,7 +6230,7 @@
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>39</v>
@@ -5265,7 +6252,7 @@
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>39</v>
@@ -5287,7 +6274,7 @@
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>39</v>
@@ -5309,7 +6296,7 @@
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>39</v>
@@ -5331,7 +6318,7 @@
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>39</v>
@@ -5346,14 +6333,14 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
       <c r="N205" s="1"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
+      <c r="O205" s="1"/>
+      <c r="P205" s="1"/>
     </row>
     <row r="206" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>39</v>
@@ -5368,14 +6355,14 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
       <c r="N206" s="1"/>
-      <c r="O206" s="1"/>
-      <c r="P206" s="1"/>
+      <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
     </row>
     <row r="207" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>39</v>
@@ -5397,7 +6384,7 @@
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>39</v>
@@ -5419,7 +6406,7 @@
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>39</v>
@@ -5441,7 +6428,7 @@
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>39</v>
@@ -5463,7 +6450,7 @@
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>39</v>
@@ -5481,6 +6468,28 @@
       <c r="O211" s="1"/>
       <c r="P211" s="1"/>
     </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+      <c r="G212" s="1"/>
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+      <c r="J212" s="1"/>
+      <c r="K212" s="1"/>
+      <c r="L212" s="1"/>
+      <c r="M212" s="1"/>
+      <c r="N212" s="1"/>
+      <c r="O212" s="1"/>
+      <c r="P212" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
